--- a/AAII_Financials/Quarterly/SWDHY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SWDHY_QTR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Quarterly/SWDHY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SWDHY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
   <si>
     <t>SWDHY</t>
   </si>
@@ -656,61 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -738,8 +745,14 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -767,8 +780,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,8 +815,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,8 +834,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -838,8 +865,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,8 +900,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -896,8 +935,14 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +970,14 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,8 +986,10 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -964,8 +1017,14 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -993,8 +1052,14 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,8 +1071,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1035,8 +1102,14 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1064,8 +1137,14 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1093,8 +1172,14 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1122,8 +1207,14 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1242,14 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,8 +1277,14 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1209,8 +1312,14 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1238,8 +1347,14 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1382,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1417,14 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1452,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,8 +1487,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1383,8 +1522,14 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1412,8 +1557,14 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,8 +1592,14 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1470,42 +1627,54 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1686,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,269 +1701,325 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1143700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1190100</v>
+      </c>
+      <c r="F41" s="3">
         <v>1194200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1201900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1285300</v>
       </c>
-      <c r="G41" s="3">
-        <v>432900</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
         <v>1435700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1515800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1312700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1293600</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>152500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>158700</v>
+      </c>
+      <c r="F42" s="3">
         <v>96500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>97100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>100400</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>103300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>109000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>151100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2533700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2636500</v>
+      </c>
+      <c r="F43" s="3">
         <v>2348300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2363400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2399600</v>
       </c>
-      <c r="G43" s="3">
-        <v>448000</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>2619600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2765700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2382000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2175800</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2485600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2586500</v>
+      </c>
+      <c r="F44" s="3">
         <v>2536400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2552700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2290000</v>
       </c>
-      <c r="G44" s="3">
-        <v>225700</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>2415800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2550500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2362700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2172100</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>470900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>490000</v>
+      </c>
+      <c r="F45" s="3">
         <v>491800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>495000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>488100</v>
       </c>
-      <c r="G45" s="3">
-        <v>11700</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>412600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>435600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>486100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>413500</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6812100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7088500</v>
+      </c>
+      <c r="F46" s="3">
         <v>6692100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>6735100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6582700</v>
       </c>
-      <c r="G46" s="3">
-        <v>1156600</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3">
         <v>7023800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7415600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>6731100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6239300</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>406200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>422700</v>
+      </c>
+      <c r="F47" s="3">
         <v>533800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>537200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>575700</v>
       </c>
-      <c r="G47" s="3">
-        <v>31500</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
         <v>574000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>606000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>534100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>495600</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1757100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1828400</v>
+      </c>
+      <c r="F48" s="3">
         <v>1713700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1724700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1735200</v>
       </c>
-      <c r="G48" s="3">
-        <v>129000</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>1509000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1593200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1512100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1418800</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>75900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>79000</v>
+      </c>
+      <c r="F49" s="3">
         <v>79700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>80200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>81400</v>
       </c>
-      <c r="G49" s="3">
-        <v>56200</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3">
         <v>79100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>83600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>82400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>78200</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2047,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +2082,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>245600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>255600</v>
+      </c>
+      <c r="F52" s="3">
         <v>251800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>253400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>273200</v>
       </c>
-      <c r="G52" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>278800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>294400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>309800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>330200</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2152,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9591300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9980500</v>
+      </c>
+      <c r="F54" s="3">
         <v>9541100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>9602400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>9471400</v>
       </c>
-      <c r="G54" s="3">
-        <v>1406500</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3">
         <v>9679800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10219700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9338600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>8724400</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2206,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,182 +2221,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3731600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3883000</v>
+      </c>
+      <c r="F57" s="3">
         <v>3449200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3471400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3746500</v>
       </c>
-      <c r="G57" s="3">
-        <v>383400</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
         <v>3927700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>4146800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1808000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1596600</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1291700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1344100</v>
+      </c>
+      <c r="F58" s="3">
         <v>1543700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1553600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1169400</v>
       </c>
-      <c r="G58" s="3">
-        <v>47800</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3">
         <v>1457700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1539000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1370100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1341200</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>95400</v>
+      </c>
+      <c r="F59" s="3">
         <v>81200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>81700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>80400</v>
       </c>
-      <c r="G59" s="3">
-        <v>71400</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>77600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>82000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1972800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1856300</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5114900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5322400</v>
+      </c>
+      <c r="F60" s="3">
         <v>5074100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5106700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4996300</v>
       </c>
-      <c r="G60" s="3">
-        <v>533200</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3">
         <v>5463100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5767800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5150900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4794100</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>955700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>994500</v>
+      </c>
+      <c r="F61" s="3">
         <v>1079400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1086400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1010700</v>
       </c>
-      <c r="G61" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>940400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>992800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>856400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>744700</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>245800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>255800</v>
+      </c>
+      <c r="F62" s="3">
         <v>178300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>179500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>151700</v>
       </c>
-      <c r="G62" s="3">
-        <v>6200</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>129500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>136700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>65400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>74800</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2462,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2497,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2532,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6421300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6681900</v>
+      </c>
+      <c r="F66" s="3">
         <v>6442600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6484000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6262100</v>
       </c>
-      <c r="G66" s="3">
-        <v>556100</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3">
         <v>6638400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7008700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6164200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5700100</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2586,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2617,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2652,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2687,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2722,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2397000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2494300</v>
+      </c>
+      <c r="F72" s="3">
         <v>2328200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2343200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2347200</v>
       </c>
-      <c r="G72" s="3">
-        <v>514500</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>2197600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2320200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2270300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2792,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2827,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2862,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2498700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2600000</v>
+      </c>
+      <c r="F76" s="3">
         <v>2458700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2474500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2558100</v>
       </c>
-      <c r="G76" s="3">
-        <v>855000</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3">
         <v>2463400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2600700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2590500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2461200</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,42 +2932,54 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2618,8 +3007,14 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +3026,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>34300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>36200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>109200</v>
       </c>
-      <c r="G83" s="3">
-        <v>-71300</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>37800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>40000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>97600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>-51800</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3092,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3127,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3162,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3197,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3232,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>140600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>146300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-176000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-177100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>316500</v>
       </c>
-      <c r="G89" s="3">
-        <v>-58100</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3">
         <v>45200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>47700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>315100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>130200</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3286,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-45500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-45800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-198600</v>
       </c>
-      <c r="G91" s="3">
-        <v>67900</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3">
         <v>-59200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-62500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-104700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-74600</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3352,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3387,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>58700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-55500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-55900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>15400</v>
       </c>
-      <c r="G94" s="3">
-        <v>-21100</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3">
         <v>-21200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-22300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-366400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-91100</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,23 +3441,25 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F96" s="3">
         <v>7600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>7700</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
-        <v>34100</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>4</v>
       </c>
@@ -3002,11 +3469,17 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3507,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3542,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,91 +3577,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-219900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-228800</v>
+      </c>
+      <c r="F100" s="3">
         <v>202800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>204100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-219800</v>
       </c>
-      <c r="G100" s="3">
-        <v>-224200</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3">
         <v>67600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>71400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>29000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-129600</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3">
         <v>1900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>700</v>
       </c>
-      <c r="G101" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-2100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-30000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-30200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>132000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-306200</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>93600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>98800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-21600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-87100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SWDHY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SWDHY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="92">
   <si>
     <t>SWDHY</t>
   </si>
@@ -656,68 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -751,8 +766,20 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -786,8 +813,20 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -821,8 +860,20 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,8 +887,12 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -871,8 +926,20 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,8 +973,20 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -941,8 +1020,20 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -976,8 +1067,20 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,8 +1091,12 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1023,8 +1130,20 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1058,8 +1177,20 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,8 +1204,12 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1108,8 +1243,20 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1143,8 +1290,20 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1178,8 +1337,20 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1213,8 +1384,20 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1248,8 +1431,20 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,8 +1478,20 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1318,8 +1525,20 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1353,8 +1572,20 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1619,20 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1666,20 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1713,20 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,8 +1760,20 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1528,8 +1807,20 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1563,8 +1854,20 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,8 +1901,20 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1633,48 +1948,72 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +2027,12 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,323 +2046,435 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1328800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1305500</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1483400</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1464500</v>
+      </c>
+      <c r="H41" s="3">
         <v>1143700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>1190100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>1194200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>1201900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>1285300</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>1435700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>1515800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>1312700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>1293600</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>212700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>209000</v>
+      </c>
+      <c r="F42" s="3">
+        <v>211500</v>
+      </c>
+      <c r="G42" s="3">
+        <v>208800</v>
+      </c>
+      <c r="H42" s="3">
         <v>152500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="I42" s="3">
         <v>158700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="J42" s="3">
         <v>96500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="K42" s="3">
         <v>97100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="L42" s="3">
         <v>100400</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>103300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="O42" s="3">
         <v>109000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="P42" s="3">
         <v>151100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="Q42" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2565100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2520100</v>
+      </c>
+      <c r="F43" s="3">
+        <v>2619000</v>
+      </c>
+      <c r="G43" s="3">
+        <v>2585500</v>
+      </c>
+      <c r="H43" s="3">
         <v>2533700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="I43" s="3">
         <v>2636500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>2348300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>2363400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>2399600</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>2619600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>2765700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>2382000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>2175800</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3056000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3002400</v>
+      </c>
+      <c r="F44" s="3">
+        <v>2766500</v>
+      </c>
+      <c r="G44" s="3">
+        <v>2731200</v>
+      </c>
+      <c r="H44" s="3">
         <v>2485600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="I44" s="3">
         <v>2586500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="J44" s="3">
         <v>2536400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="K44" s="3">
         <v>2552700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>2290000</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>2415800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>2550500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>2362700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>2172100</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>425500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>418000</v>
+      </c>
+      <c r="F45" s="3">
+        <v>399200</v>
+      </c>
+      <c r="G45" s="3">
+        <v>394100</v>
+      </c>
+      <c r="H45" s="3">
         <v>470900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="I45" s="3">
         <v>490000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="J45" s="3">
         <v>491800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="K45" s="3">
         <v>495000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>488100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>412600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>435600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>486100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>413500</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7615700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7482200</v>
+      </c>
+      <c r="F46" s="3">
+        <v>7513600</v>
+      </c>
+      <c r="G46" s="3">
+        <v>7417600</v>
+      </c>
+      <c r="H46" s="3">
         <v>6812100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>7088500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>6692100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>6735100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>6582700</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>7023800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>7415600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>6731100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>6239300</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>572700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>562700</v>
+      </c>
+      <c r="F47" s="3">
+        <v>428700</v>
+      </c>
+      <c r="G47" s="3">
+        <v>423200</v>
+      </c>
+      <c r="H47" s="3">
         <v>406200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="I47" s="3">
         <v>422700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="J47" s="3">
         <v>533800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="K47" s="3">
         <v>537200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="L47" s="3">
         <v>575700</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>574000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>606000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>534100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>495600</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2008900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1973700</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1857500</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1833800</v>
+      </c>
+      <c r="H48" s="3">
         <v>1757100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
         <v>1828400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>1713700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>1724700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>1735200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3">
         <v>1509000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>1593200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>1512100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>1418800</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>109200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>107300</v>
+      </c>
+      <c r="F49" s="3">
+        <v>107200</v>
+      </c>
+      <c r="G49" s="3">
+        <v>105800</v>
+      </c>
+      <c r="H49" s="3">
         <v>75900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="I49" s="3">
         <v>79000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="J49" s="3">
         <v>79700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="K49" s="3">
         <v>80200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>81400</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N49" s="3">
         <v>79100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>83600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>82400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="Q49" s="3">
         <v>78200</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2508,20 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,43 +2555,67 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>251300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>246900</v>
+      </c>
+      <c r="F52" s="3">
+        <v>225900</v>
+      </c>
+      <c r="G52" s="3">
+        <v>223000</v>
+      </c>
+      <c r="H52" s="3">
         <v>245600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="I52" s="3">
         <v>255600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="J52" s="3">
         <v>251800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="K52" s="3">
         <v>253400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>273200</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>278800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>294400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>309800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>330200</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,43 +2649,67 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10937900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10746200</v>
+      </c>
+      <c r="F54" s="3">
+        <v>10473600</v>
+      </c>
+      <c r="G54" s="3">
+        <v>10339800</v>
+      </c>
+      <c r="H54" s="3">
         <v>9591300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>9980500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>9541100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>9602400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>9471400</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>9679800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>10219700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>9338600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>8724400</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2723,12 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,218 +2742,294 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4300400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4225100</v>
+      </c>
+      <c r="F57" s="3">
+        <v>4079700</v>
+      </c>
+      <c r="G57" s="3">
+        <v>4027600</v>
+      </c>
+      <c r="H57" s="3">
         <v>3731600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>3883000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>3449200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>3471400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>3746500</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>3927700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>4146800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>1808000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>1596600</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1825200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1793200</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1819800</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1796600</v>
+      </c>
+      <c r="H58" s="3">
         <v>1291700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="I58" s="3">
         <v>1344100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="J58" s="3">
         <v>1543700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="K58" s="3">
         <v>1553600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="L58" s="3">
         <v>1169400</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N58" s="3">
         <v>1457700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>1539000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>1370100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="Q58" s="3">
         <v>1341200</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>235500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>231300</v>
+      </c>
+      <c r="F59" s="3">
+        <v>91900</v>
+      </c>
+      <c r="G59" s="3">
+        <v>90700</v>
+      </c>
+      <c r="H59" s="3">
         <v>91700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="I59" s="3">
         <v>95400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="J59" s="3">
         <v>81200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="K59" s="3">
         <v>81700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>80400</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>77600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>82000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>1972800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>1856300</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6361100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6249600</v>
+      </c>
+      <c r="F60" s="3">
+        <v>5991400</v>
+      </c>
+      <c r="G60" s="3">
+        <v>5914800</v>
+      </c>
+      <c r="H60" s="3">
         <v>5114900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>5322400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>5074100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>5106700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>4996300</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>5463100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>5767800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>5150900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>4794100</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>785500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>771700</v>
+      </c>
+      <c r="F61" s="3">
+        <v>874100</v>
+      </c>
+      <c r="G61" s="3">
+        <v>863000</v>
+      </c>
+      <c r="H61" s="3">
         <v>955700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>994500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>1079400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="K61" s="3">
         <v>1086400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>1010700</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>940400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>992800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>856400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="Q61" s="3">
         <v>744700</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>379600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>372900</v>
+      </c>
+      <c r="F62" s="3">
+        <v>329900</v>
+      </c>
+      <c r="G62" s="3">
+        <v>325600</v>
+      </c>
+      <c r="H62" s="3">
         <v>245800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="I62" s="3">
         <v>255800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="J62" s="3">
         <v>178300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="K62" s="3">
         <v>179500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>151700</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>129500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>136700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>65400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>74800</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +3063,20 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +3110,20 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,43 +3157,67 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7641000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7507000</v>
+      </c>
+      <c r="F66" s="3">
+        <v>7302400</v>
+      </c>
+      <c r="G66" s="3">
+        <v>7209100</v>
+      </c>
+      <c r="H66" s="3">
         <v>6421300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>6681900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>6442600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>6484000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>6262100</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>6638400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>7008700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>6164200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>5700100</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +3231,12 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +3270,20 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +3317,20 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +3364,20 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,43 +3411,67 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2525900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2481600</v>
+      </c>
+      <c r="F72" s="3">
+        <v>2444200</v>
+      </c>
+      <c r="G72" s="3">
+        <v>2413000</v>
+      </c>
+      <c r="H72" s="3">
         <v>2397000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="I72" s="3">
         <v>2494300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>2328200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>2343200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>2347200</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>2197600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>2320200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>2270300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +3505,20 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3552,20 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,43 +3599,67 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2499000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2455200</v>
+      </c>
+      <c r="F76" s="3">
+        <v>2425900</v>
+      </c>
+      <c r="G76" s="3">
+        <v>2395000</v>
+      </c>
+      <c r="H76" s="3">
         <v>2498700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>2600000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>2458700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>2474500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>2558100</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N76" s="3">
         <v>2463400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>2600700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>2590500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>2461200</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,48 +3693,72 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3013,8 +3792,20 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,43 +3819,59 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F83" s="3">
+        <v>21300</v>
+      </c>
+      <c r="G83" s="3">
+        <v>21500</v>
+      </c>
+      <c r="H83" s="3">
         <v>85000</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="I83" s="3">
         <v>34300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3">
         <v>36200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="K83" s="3">
+        <v>36200</v>
+      </c>
+      <c r="L83" s="3">
         <v>109200</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>37800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="O83" s="3">
         <v>40000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="P83" s="3">
         <v>97600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="Q83" s="3">
         <v>-51800</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3905,20 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3952,20 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3999,20 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +4046,20 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,43 +4093,67 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F89" s="3">
+        <v>149600</v>
+      </c>
+      <c r="G89" s="3">
+        <v>147700</v>
+      </c>
+      <c r="H89" s="3">
         <v>140600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="I89" s="3">
         <v>146300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="J89" s="3">
         <v>-176000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>-177100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>316500</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N89" s="3">
         <v>45200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>47700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>315100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>130200</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,43 +4167,59 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-53500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-45200</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="H91" s="3">
         <v>-38900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="I91" s="3">
         <v>-40500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="J91" s="3">
         <v>-45500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="K91" s="3">
         <v>-45800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-198600</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N91" s="3">
         <v>-59200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-62500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>-104700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-74600</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +4253,20 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,43 +4300,67 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-75300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-77700</v>
+      </c>
+      <c r="H94" s="3">
         <v>56400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="I94" s="3">
         <v>58700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="J94" s="3">
         <v>-55500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="K94" s="3">
         <v>-55900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>15400</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3">
         <v>-21200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>-22300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>-366400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>-91100</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,43 +4374,59 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>6100</v>
+        <v>20200</v>
       </c>
       <c r="E96" s="3">
-        <v>6300</v>
-      </c>
-      <c r="F96" s="3">
+        <v>19900</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>7600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="K96" s="3">
         <v>7700</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +4460,20 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +4507,20 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,109 +4554,157 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="F100" s="3">
+        <v>87700</v>
+      </c>
+      <c r="G100" s="3">
+        <v>86600</v>
+      </c>
+      <c r="H100" s="3">
         <v>-219900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="I100" s="3">
         <v>-228800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="J100" s="3">
         <v>202800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="K100" s="3">
         <v>204100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>-219800</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3">
         <v>67600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>71400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>29000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>-129600</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>300</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H101" s="3">
         <v>19900</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="I101" s="3">
         <v>1900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="K101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L101" s="3">
         <v>700</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3">
         <v>-1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="O101" s="3">
         <v>-2100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="Q101" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-95300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="F102" s="3">
+        <v>159100</v>
+      </c>
+      <c r="G102" s="3">
+        <v>157000</v>
+      </c>
+      <c r="H102" s="3">
         <v>-22600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="I102" s="3">
         <v>-23500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="J102" s="3">
         <v>-30000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>-30200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>132000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>93600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>98800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>-21600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>-87100</v>
       </c>
     </row>
